--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.70 ± 0.08</t>
+          <t>0.72 ± 0.07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.36 ± 0.11</t>
+          <t>0.34 ± 0.18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.45 ± 0.40</t>
+          <t>0.12 ± 0.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.39</t>
+          <t>0.94 ± 0.07</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.84 ± 0.21</t>
+          <t>0.82 ± 0.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.89 ± 0.12</t>
+          <t>0.73 ± 0.21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F4" t="n">
